--- a/Plotting/Latex/filtered_data_import_combined.xlsx
+++ b/Plotting/Latex/filtered_data_import_combined.xlsx
@@ -1179,7 +1179,7 @@
         <v>114</v>
       </c>
       <c r="H24" t="n">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -1212,7 +1212,7 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -1233,22 +1233,22 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="E26" t="n">
-        <v>858</v>
+        <v>850</v>
       </c>
       <c r="F26" t="n">
-        <v>4</v>
+        <v>746</v>
       </c>
       <c r="G26" t="n">
-        <v>734</v>
+        <v>421</v>
       </c>
       <c r="H26" t="n">
-        <v>1533</v>
+        <v>1112</v>
       </c>
       <c r="I26" t="n">
-        <v>7</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="27">
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1314,7 +1314,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>123</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29">
@@ -1344,10 +1344,10 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="I29" t="n">
-        <v>202</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
